--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_266_Gabon.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_266_Gabon.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf3d84d3faed24ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4fde2ba5de2e41c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8db866bb14914bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6ff452f916264de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R95ab65818d3745bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R798df5eabab64d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd176dc11a1774db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R969e52c95ddc464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R23e18c5975604f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re789490c672c4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7546f76eb4ff45d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9d441e48d8334648"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ266CommercialTable" displayName="EEZ266CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ266CommercialTable" displayName="EEZ266CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ266FunctionalTable" displayName="EEZ266FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ266FunctionalTable" displayName="EEZ266FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ266ValidationTable" displayName="EEZ266ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ266ValidationTable" displayName="EEZ266ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13022,7 +12976,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R253e5b71fef547e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0926ab33af64f97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13032,20 +12986,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13053,660 +12997,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>70.7333001625</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>70.7333001625</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$185,A2,'Species'!$U$2:$U$185))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9112.214222411649</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>9112.214222411649</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>813.9195741233</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.230248357459641</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1699.2150949229087</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>813.9195741233</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2072.287532508388</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$185,A3,'Species'!$U$2:$U$185))</x:f>
-        <x:v>1686675.3859202513</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.230248357459641</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1699.2150949229087</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1383024.4264035367</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>303650.95951671456</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.21955574588537</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.21955574588537005</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>274.7023969516</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2576611908423563</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>180.99275504061572</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>274.7023969516</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>223.89390133540357</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$185,A4,'Species'!$U$2:$U$185))</x:f>
-        <x:v>61504.1913596804</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2576611908423563</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>180.99275504061572</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>49719.14364053092</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>11785.04771914948</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2370323954964972</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2370323954964972</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>553.746176726</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5395215281439745</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>346.35505313552557</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>553.746176726</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>359.4180849560196</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$185,A5,'Species'!$U$2:$U$185))</x:f>
-        <x:v>199026.3903905765</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5395215281439745</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>346.35505313552557</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>191792.78646352788</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7233.603927048622</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0377157246652975</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.03771572466529753</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>25595.516703584</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.6000613376030497</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>39.81634012105802</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>25595.516703584</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>41.78766957355618</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$185,A6,'Species'!$U$2:$U$185))</x:f>
-        <x:v>1069576.994573806</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.6000613376030497</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>39.81634012105802</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1019119.7986441222</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>50457.195929683745</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.049510563916837</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.049510563916836885</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>20.9791763667</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.056058593215497</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>113.77807801464144</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>20.9791763667</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>114.35078461136725</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$185,A7,'Species'!$U$2:$U$185))</x:f>
-        <x:v>2398.9852780323977</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.056058593215497</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>113.77807801464144</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2386.9703653333145</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>12.014912699083197</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.005033540790275</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.005033540790275143</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>60057.80904621059</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3013506073204058</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>200.14770163674137</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>60057.80904621059</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>214.67008944592328</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$185,A8,'Species'!$U$2:$U$185))</x:f>
-        <x:v>12892615.239876207</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3013506073204058</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>200.14770163674137</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12020432.445937345</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>872182.7939388622</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0725583541076047</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07255835410760465</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>46820.3544578503</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.738442797675607</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>547.5739734810027</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>46820.3544578503</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>701.965086111441</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$185,A9,'Species'!$U$2:$U$185))</x:f>
-        <x:v>32866254.148773074</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.738442797675607</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>547.5739734810027</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>25637607.530274063</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7228646.618499011</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2819548044786586</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.28195480447865867</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>11.4066832511</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.741413149470635</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>551.3319355912079</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>11.4066832511</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>618.3192742592439</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$185,A10,'Species'!$U$2:$U$185))</x:f>
-        <x:v>7052.972109525225</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.741413149470635</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>551.3319355912079</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6288.868755504775</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>764.1033540204498</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1215009223004717</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1215009223004717</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2459.8912213952</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.230863500652523</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1701.6236017215765</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2459.8912213952</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1949.9296852820698</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$185,A11,'Species'!$U$2:$U$185))</x:f>
-        <x:v>4796614.915163268</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.230863500652523</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1701.6236017215765</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4185808.959993788</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>610805.9551694803</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1459230368627207</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.14592303686272073</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>22228.474061265202</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.427260556447661</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2674.6105690883683</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>22228.474061265202</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2678.4048314539373</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$185,A12,'Species'!$U$2:$U$185))</x:f>
-        <x:v>59536852.32154124</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.427260556447661</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2674.6105690883683</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>59452511.658966556</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>84340.66257468611</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.001418622362979</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0014186223629791082</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38f7a10c3bae4641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R664cd11efbb846c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13716,20 +13231,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13737,1254 +13242,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1170.841336781</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8381442200575284</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>688.8810212541748</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1170.841336781</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>725.0925793573995</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$185,A2,'Species'!$U$2:$U$185))</x:f>
-        <x:v>848968.364904801</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8381442200575284</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>688.8810212541748</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>806570.3758082986</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>42397.989096502424</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0525657653295455</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0525657653295456</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9.8167683724</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9.8167683724</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$185,A3,'Species'!$U$2:$U$185))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>21476.749116338426</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>21476.749116338426</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3370.9331029818</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.072594687523433</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1181.9379777589297</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3370.9331029818</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1253.8782549075113</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$185,A4,'Species'!$U$2:$U$185))</x:f>
-        <x:v>4226739.716576781</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.072594687523433</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1181.9379777589297</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3984233.8548989426</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>242505.8616778385</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0608663724343534</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.060866372434353375</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6451.583207325601</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8330175357322855</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>680.7968470241995</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6451.583207325601</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>714.0999594101455</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$185,A5,'Species'!$U$2:$U$185))</x:f>
-        <x:v>4607075.306482388</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8330175357322855</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>680.7968470241995</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4392217.505861541</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>214857.80062084645</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0489178416902425</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04891784169024246</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>23104.827459686607</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.42773595841434</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2677.5399438925438</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>23104.827459686607</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2680.2150409490255</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$185,A6,'Species'!$U$2:$U$185))</x:f>
-        <x:v>61925906.075984105</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.42773595841434</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2677.5399438925438</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>61864098.42005618</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>61807.6559279263</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0009990876373605</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0009990876373604182</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>278.9479823801</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5057171528017252</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>320.4181826092422</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>278.9479823801</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>334.23460232258554</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$185,A7,'Species'!$U$2:$U$185))</x:f>
-        <x:v>93234.06795950032</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5057171528017252</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>320.4181826092422</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>89380.00555674655</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3854.0624027537706</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0431199615478526</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.043119961547852685</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>260.7865939385</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5874611992379823</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>386.7774975924426</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>260.7865939385</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>423.525684475496</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$185,A8,'Species'!$U$2:$U$185))</x:f>
-        <x:v>110449.82069983645</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5874611992379823</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>386.7774975924426</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>100866.3862091895</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>9583.434490646949</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0950111811359198</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.09501118113591982</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2172.7447692130004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.325587250528008</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2116.348820748033</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2172.7447692130004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2162.3377163487053</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$185,A9,'Species'!$U$2:$U$185))</x:f>
-        <x:v>4698207.962468634</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.325587250528008</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2116.348820748033</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4598285.830110391</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>99922.13235824369</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0217303003880132</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.021730300388013258</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>34.0753139212</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.1209660650220017</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>132.1192394591314</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>34.0753139212</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>133.6249263536721</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$185,A10,'Species'!$U$2:$U$185))</x:f>
-        <x:v>4553.311313198607</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.1209660650220017</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>132.1192394591314</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4502.004559600096</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>51.30675359851102</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0113964241748943</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.011396424174894327</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>515.3262124185</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.4652438616844305</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2919.0656451062437</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>515.3262124185</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3003.154540479302</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$185,A11,'Species'!$U$2:$U$185))</x:f>
-        <x:v>1547604.2546526194</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.4652438616844305</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2919.0656451062437</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1504271.0426935656</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>43333.21195905376</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0288067846346765</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.028806784634676473</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>229.34865818120002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.081534120252449</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1206.518874369077</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>229.34865818120002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1207.4625301439341</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$185,A12,'Species'!$U$2:$U$185))</x:f>
-        <x:v>276929.9110925881</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.081534120252449</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1206.518874369077</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>276713.4849068396</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>216.42618574848166</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0007821309677818</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0007821309677818747</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1998.1852355234</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.691991514092145</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>492.0299215566063</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1998.1852355234</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>650.2931883711279</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$185,A13,'Species'!$U$2:$U$185))</x:f>
-        <x:v>1299406.2477646251</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.691991514092145</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>492.0299215566063</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>983166.9246901474</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>316239.3230744777</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.321653744784125</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.321653744784125</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>62057.0863845269</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.315916704809625</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>206.9744345628028</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>62057.0863845269</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>232.96631805062574</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$185,A14,'Species'!$U$2:$U$185))</x:f>
-        <x:v>14457210.92395285</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.315916704809625</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>206.9744345628028</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>12844230.365052463</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1612980.558900386</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1255801642493974</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.1255801642493974</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>43319.56737562871</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2801970756887684</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>190.63255808946187</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>43319.56737562871</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>391.30678336573555</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$185,A15,'Species'!$U$2:$U$185))</x:f>
-        <x:v>16951240.566552527</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2801970756887684</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>190.63255808946187</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8258119.944144896</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8693120.62240763</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.052675509826078</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.0526755098260778</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3134.3103796638</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9526523270481277</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>89.6710648462882</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3134.3103796638</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>342.06836096977383</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$185,A16,'Species'!$U$2:$U$185))</x:f>
-        <x:v>1072148.4143421457</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9526523270481277</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>89.6710648462882</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>281056.94930322684</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>791091.4650389189</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>3.814701671672333</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>2.8147016716723336</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>21.0031168871</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0553449768221284</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>113.591275662335</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>21.0031168871</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>114.25112083935717</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$185,A17,'Species'!$U$2:$U$185))</x:f>
-        <x:v>2399.629645471205</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0553449768221284</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>113.591275662335</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2385.770840090819</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>13.858805380386002</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0058089423961014</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.005808942396101396</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>240.6270830304</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.277018651628423</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>189.24248907988212</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>240.6270830304</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>236.67693315837943</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$185,A18,'Species'!$U$2:$U$185))</x:f>
-        <x:v>56950.8800464818</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.277018651628423</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>189.24248907988212</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>45536.86813270436</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>11414.011913777438</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2506543023669199</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.25065430236691993</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>448.0662263741</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.525307144119911</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>335.202419037835</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>448.0662263741</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>346.18115278163594</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$185,A19,'Species'!$U$2:$U$185))</x:f>
-        <x:v>155112.08276870337</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.525307144119911</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>335.202419037835</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>150192.8829697525</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>4919.199798950867</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0327525492665426</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.032752549266542474</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>9526.503898120498</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.773024488163186</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>59.29587582570811</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>9526.503898120498</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>59.552737067745184</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$185,A20,'Species'!$U$2:$U$185))</x:f>
-        <x:v>567329.3818196196</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.773024488163186</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>59.29587582570811</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>564882.3921960773</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2446.989623542293</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0043318567853199</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.004331856785319862</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1.0070464036</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1.0070464036</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$185,A21,'Species'!$U$2:$U$185))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>540.8159391535105</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>540.8159391535105</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>553.746176726</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.5395215281439745</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>346.35505313552557</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>553.746176726</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>359.4180849560196</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$185,A22,'Species'!$U$2:$U$185))</x:f>
-        <x:v>199026.3903905765</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.5395215281439745</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>346.35505313552557</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>191792.78646352788</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>7233.603927048622</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0377157246652975</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.03771572466529753</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>8.1984698021</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>630.9573444801937</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>8.1984698021</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>630.9573444801931</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$185,A23,'Species'!$U$2:$U$185))</x:f>
-        <x:v>5172.88473513407</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.8000000000000003</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>630.9573444801937</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>5172.884735134075</x:v>
       </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>-4.547473508864641e-12</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>-8.790981708868052e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb067e799b4ab4c50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2312e7184ef74e90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15159,7 +13850,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15258,7 +13949,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>113127683.75920808</x:v>
+        <x:v>103957804.80366671</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15272,7 +13963,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>113127683.75920807</x:v>
+        <x:v>100969694.24424481</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15286,7 +13977,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-9169878.955541342</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15300,7 +13991,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.4901161193847656e-8</x:v>
+        <x:v>-12157989.51496324</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15311,9 +14002,9 @@
         <x:v>EEZ_266</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15325,47 +14016,19 @@
         <x:v>EEZ_266</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_266</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_266</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd13cdd8b8a2740d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra87eac676d5f4d72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15412,7 +14075,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
